--- a/artfynd/A 17855-2024 artfynd.xlsx
+++ b/artfynd/A 17855-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117753472</v>
+        <v>117753462</v>
       </c>
       <c r="B2" t="n">
-        <v>57303</v>
+        <v>90499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422718</v>
+        <v>422897</v>
       </c>
       <c r="R2" t="n">
-        <v>7043066</v>
+        <v>7043001</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117753483</v>
+        <v>117753473</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>57303</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422869</v>
+        <v>422877</v>
       </c>
       <c r="R3" t="n">
-        <v>7042991</v>
+        <v>7042938</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117753464</v>
+        <v>117753484</v>
       </c>
       <c r="B4" t="n">
-        <v>91190</v>
+        <v>78480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422700</v>
+        <v>423094</v>
       </c>
       <c r="R4" t="n">
-        <v>7043035</v>
+        <v>7042639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117753484</v>
+        <v>117753483</v>
       </c>
       <c r="B5" t="n">
         <v>78480</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423094</v>
+        <v>422869</v>
       </c>
       <c r="R5" t="n">
-        <v>7042639</v>
+        <v>7042991</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117753473</v>
+        <v>117753464</v>
       </c>
       <c r="B6" t="n">
-        <v>57303</v>
+        <v>91190</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422877</v>
+        <v>422700</v>
       </c>
       <c r="R6" t="n">
-        <v>7042938</v>
+        <v>7043035</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117753481</v>
+        <v>117753472</v>
       </c>
       <c r="B7" t="n">
-        <v>90517</v>
+        <v>57303</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422693</v>
+        <v>422718</v>
       </c>
       <c r="R7" t="n">
-        <v>7043052</v>
+        <v>7043066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117753462</v>
+        <v>117753481</v>
       </c>
       <c r="B8" t="n">
-        <v>90499</v>
+        <v>90517</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422897</v>
+        <v>422693</v>
       </c>
       <c r="R8" t="n">
-        <v>7043001</v>
+        <v>7043052</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 17855-2024 artfynd.xlsx
+++ b/artfynd/A 17855-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117753462</v>
+        <v>117753484</v>
       </c>
       <c r="B2" t="n">
-        <v>90499</v>
+        <v>78482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422897</v>
+        <v>423094</v>
       </c>
       <c r="R2" t="n">
-        <v>7043001</v>
+        <v>7042639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>117753473</v>
       </c>
       <c r="B3" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117753484</v>
+        <v>117753472</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>57304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423094</v>
+        <v>422718</v>
       </c>
       <c r="R4" t="n">
-        <v>7042639</v>
+        <v>7043066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117753483</v>
+        <v>117753462</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422869</v>
+        <v>422897</v>
       </c>
       <c r="R5" t="n">
-        <v>7042991</v>
+        <v>7043001</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117753464</v>
+        <v>117753481</v>
       </c>
       <c r="B6" t="n">
-        <v>91190</v>
+        <v>90519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422700</v>
+        <v>422693</v>
       </c>
       <c r="R6" t="n">
-        <v>7043035</v>
+        <v>7043052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117753472</v>
+        <v>117753464</v>
       </c>
       <c r="B7" t="n">
-        <v>57303</v>
+        <v>91192</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422718</v>
+        <v>422700</v>
       </c>
       <c r="R7" t="n">
-        <v>7043066</v>
+        <v>7043035</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117753481</v>
+        <v>117753483</v>
       </c>
       <c r="B8" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422693</v>
+        <v>422869</v>
       </c>
       <c r="R8" t="n">
-        <v>7043052</v>
+        <v>7042991</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 17855-2024 artfynd.xlsx
+++ b/artfynd/A 17855-2024 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117753464</v>
+        <v>117753483</v>
       </c>
       <c r="B7" t="n">
-        <v>91192</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422700</v>
+        <v>422869</v>
       </c>
       <c r="R7" t="n">
-        <v>7043035</v>
+        <v>7042991</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117753483</v>
+        <v>117753464</v>
       </c>
       <c r="B8" t="n">
-        <v>78482</v>
+        <v>91192</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422869</v>
+        <v>422700</v>
       </c>
       <c r="R8" t="n">
-        <v>7042991</v>
+        <v>7043035</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
